--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/42.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/42.xlsx
@@ -426,13 +426,13 @@
         <v>-19.61347192934271</v>
       </c>
       <c r="E2">
-        <v>-14.6437647031033</v>
+        <v>-14.48225214914573</v>
       </c>
       <c r="F2">
-        <v>1.119372990091722</v>
+        <v>0.9623485485759012</v>
       </c>
       <c r="G2">
-        <v>-17.04309016284666</v>
+        <v>-16.80218010868112</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.84665366614278</v>
       </c>
       <c r="E3">
-        <v>-16.92847040945315</v>
+        <v>-15.25740463046069</v>
       </c>
       <c r="F3">
-        <v>0.9951740210852147</v>
+        <v>1.180768517315564</v>
       </c>
       <c r="G3">
-        <v>-15.82829706412048</v>
+        <v>-16.98779412070421</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.07107283419922</v>
       </c>
       <c r="E4">
-        <v>-14.78272998497668</v>
+        <v>-14.99024277790416</v>
       </c>
       <c r="F4">
-        <v>1.770214356806633</v>
+        <v>1.187811257521523</v>
       </c>
       <c r="G4">
-        <v>-16.18957689882115</v>
+        <v>-15.53960590618665</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.36399393654274</v>
       </c>
       <c r="E5">
-        <v>-16.05039929936586</v>
+        <v>-15.40086668702368</v>
       </c>
       <c r="F5">
-        <v>1.045417091252531</v>
+        <v>1.365560074646785</v>
       </c>
       <c r="G5">
-        <v>-15.81228395534703</v>
+        <v>-16.05892952965935</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.71852214062244</v>
       </c>
       <c r="E6">
-        <v>-15.88802180687283</v>
+        <v>-15.02211417797015</v>
       </c>
       <c r="F6">
-        <v>1.664079137471628</v>
+        <v>1.395482614213097</v>
       </c>
       <c r="G6">
-        <v>-14.84350080618963</v>
+        <v>-16.06229966501833</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.15360258991597</v>
       </c>
       <c r="E7">
-        <v>-16.69779447197643</v>
+        <v>-16.06905661227747</v>
       </c>
       <c r="F7">
-        <v>1.670965090791958</v>
+        <v>1.855170676934467</v>
       </c>
       <c r="G7">
-        <v>-14.81704127096701</v>
+        <v>-14.86206137975556</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.65611789525603</v>
       </c>
       <c r="E8">
-        <v>-18.82447454935461</v>
+        <v>-16.48906351954088</v>
       </c>
       <c r="F8">
-        <v>1.676392450964169</v>
+        <v>1.759280451166439</v>
       </c>
       <c r="G8">
-        <v>-14.39266078301507</v>
+        <v>-13.82683227107945</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.21697293209938</v>
       </c>
       <c r="E9">
-        <v>-18.83346809873384</v>
+        <v>-17.96714837869647</v>
       </c>
       <c r="F9">
-        <v>1.756752856525398</v>
+        <v>1.841275241232401</v>
       </c>
       <c r="G9">
-        <v>-14.02306651319252</v>
+        <v>-12.85751777936301</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.83110144962255</v>
       </c>
       <c r="E10">
-        <v>-19.32248442140014</v>
+        <v>-17.87402031072872</v>
       </c>
       <c r="F10">
-        <v>1.772977923629075</v>
+        <v>1.502050185263018</v>
       </c>
       <c r="G10">
-        <v>-14.02605759108725</v>
+        <v>-12.11618731675401</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.48229807848877</v>
       </c>
       <c r="E11">
-        <v>-19.82996786106972</v>
+        <v>-17.9619723329057</v>
       </c>
       <c r="F11">
-        <v>2.654588997812245</v>
+        <v>1.943845538551752</v>
       </c>
       <c r="G11">
-        <v>-13.13702713924367</v>
+        <v>-13.60899175350433</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.15724180849522</v>
       </c>
       <c r="E12">
-        <v>-20.12211783320057</v>
+        <v>-19.16876537120977</v>
       </c>
       <c r="F12">
-        <v>2.357579206724815</v>
+        <v>2.44740383883671</v>
       </c>
       <c r="G12">
-        <v>-12.17505874807887</v>
+        <v>-12.14257567524754</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.832447165872</v>
       </c>
       <c r="E13">
-        <v>-20.98443891068917</v>
+        <v>-18.65423562598426</v>
       </c>
       <c r="F13">
-        <v>2.71410783352629</v>
+        <v>2.448441166211323</v>
       </c>
       <c r="G13">
-        <v>-12.71315813057755</v>
+        <v>-12.15543052357653</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.50589494859946</v>
       </c>
       <c r="E14">
-        <v>-20.88690463751197</v>
+        <v>-19.90939729516426</v>
       </c>
       <c r="F14">
-        <v>3.233444595846771</v>
+        <v>2.718586553855153</v>
       </c>
       <c r="G14">
-        <v>-12.25348888244974</v>
+        <v>-11.07747054835228</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.15749757723069</v>
       </c>
       <c r="E15">
-        <v>-20.68549169907281</v>
+        <v>-20.84846242166086</v>
       </c>
       <c r="F15">
-        <v>3.127174761508953</v>
+        <v>2.987498234590856</v>
       </c>
       <c r="G15">
-        <v>-11.47972500519251</v>
+        <v>-12.12900243853653</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.77299801048498</v>
       </c>
       <c r="E16">
-        <v>-22.78829766148256</v>
+        <v>-23.35353273017196</v>
       </c>
       <c r="F16">
-        <v>3.608257107441994</v>
+        <v>3.015195667345976</v>
       </c>
       <c r="G16">
-        <v>-11.44971159933347</v>
+        <v>-11.08500203945412</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.34694673354715</v>
       </c>
       <c r="E17">
-        <v>-23.54672648828719</v>
+        <v>-23.34669473442037</v>
       </c>
       <c r="F17">
-        <v>4.09581047574552</v>
+        <v>3.409175771635763</v>
       </c>
       <c r="G17">
-        <v>-11.65018499500958</v>
+        <v>-10.96856684229242</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.87843955376974</v>
       </c>
       <c r="E18">
-        <v>-22.32709975464538</v>
+        <v>-24.93729405877054</v>
       </c>
       <c r="F18">
-        <v>3.713933052061522</v>
+        <v>3.743825501215442</v>
       </c>
       <c r="G18">
-        <v>-11.00971030225448</v>
+        <v>-10.1539442119895</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.36755805070365</v>
       </c>
       <c r="E19">
-        <v>-26.09270250250958</v>
+        <v>-25.99387308576618</v>
       </c>
       <c r="F19">
-        <v>4.333293512589328</v>
+        <v>3.847545569029402</v>
       </c>
       <c r="G19">
-        <v>-10.79498500803181</v>
+        <v>-11.81273609153333</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.81549950639849</v>
       </c>
       <c r="E20">
-        <v>-25.54315406778275</v>
+        <v>-26.07919859301871</v>
       </c>
       <c r="F20">
-        <v>4.488026331645508</v>
+        <v>4.050689110508736</v>
       </c>
       <c r="G20">
-        <v>-10.49705577277064</v>
+        <v>-11.15566894453541</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.24247581148272</v>
       </c>
       <c r="E21">
-        <v>-26.45531100172577</v>
+        <v>-27.4467660440171</v>
       </c>
       <c r="F21">
-        <v>4.525149982009324</v>
+        <v>4.586187591696276</v>
       </c>
       <c r="G21">
-        <v>-10.54029149751352</v>
+        <v>-11.06994898888706</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.659721038999603</v>
       </c>
       <c r="E22">
-        <v>-26.19466109479228</v>
+        <v>-27.39443046991045</v>
       </c>
       <c r="F22">
-        <v>4.544620062533737</v>
+        <v>4.462479571523554</v>
       </c>
       <c r="G22">
-        <v>-10.34667093110371</v>
+        <v>-9.263791485208101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.083924886796062</v>
       </c>
       <c r="E23">
-        <v>-27.49097753575399</v>
+        <v>-26.56757640084992</v>
       </c>
       <c r="F23">
-        <v>4.395879986661579</v>
+        <v>4.4429128849383</v>
       </c>
       <c r="G23">
-        <v>-10.19309803408246</v>
+        <v>-9.669478977772549</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.530349559768059</v>
       </c>
       <c r="E24">
-        <v>-27.69568267479672</v>
+        <v>-28.03637335981578</v>
       </c>
       <c r="F24">
-        <v>4.54117075104991</v>
+        <v>4.94226486231185</v>
       </c>
       <c r="G24">
-        <v>-9.523507093309465</v>
+        <v>-9.305775823737138</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.021431303254516</v>
       </c>
       <c r="E25">
-        <v>-28.68672109747935</v>
+        <v>-26.93806897331347</v>
       </c>
       <c r="F25">
-        <v>4.606777352302904</v>
+        <v>5.117322963086781</v>
       </c>
       <c r="G25">
-        <v>-9.276272241891153</v>
+        <v>-8.414275704921261</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.56724419401928</v>
       </c>
       <c r="E26">
-        <v>-28.67647316079999</v>
+        <v>-26.61539255789691</v>
       </c>
       <c r="F26">
-        <v>4.760688227988971</v>
+        <v>5.086005178608965</v>
       </c>
       <c r="G26">
-        <v>-8.604052727959981</v>
+        <v>-9.323768638743077</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.174544432976195</v>
       </c>
       <c r="E27">
-        <v>-29.02795067090532</v>
+        <v>-28.64642220728509</v>
       </c>
       <c r="F27">
-        <v>4.926587757454915</v>
+        <v>5.033096731385964</v>
       </c>
       <c r="G27">
-        <v>-8.364591037467878</v>
+        <v>-8.687346053728044</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.854839727046008</v>
       </c>
       <c r="E28">
-        <v>-30.10265491511666</v>
+        <v>-29.59384010408883</v>
       </c>
       <c r="F28">
-        <v>4.85559180497168</v>
+        <v>4.804954392031419</v>
       </c>
       <c r="G28">
-        <v>-8.730697647564801</v>
+        <v>-8.324636063354415</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.608730038984984</v>
       </c>
       <c r="E29">
-        <v>-29.16330675899459</v>
+        <v>-29.69734517024515</v>
       </c>
       <c r="F29">
-        <v>4.624316895316396</v>
+        <v>4.984160218598885</v>
       </c>
       <c r="G29">
-        <v>-8.016473931831356</v>
+        <v>-8.696940014700852</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.436609886969692</v>
       </c>
       <c r="E30">
-        <v>-29.17993531555075</v>
+        <v>-31.09105323745282</v>
       </c>
       <c r="F30">
-        <v>4.409122935526484</v>
+        <v>4.655789882973924</v>
       </c>
       <c r="G30">
-        <v>-7.628299225169653</v>
+        <v>-7.861053750399192</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.331088095917122</v>
       </c>
       <c r="E31">
-        <v>-28.22684550505241</v>
+        <v>-28.65417495478622</v>
       </c>
       <c r="F31">
-        <v>4.588571069099012</v>
+        <v>4.402039018966723</v>
       </c>
       <c r="G31">
-        <v>-8.411984807408086</v>
+        <v>-8.712843875471512</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.294285525621912</v>
       </c>
       <c r="E32">
-        <v>-28.72314814239705</v>
+        <v>-30.52103383597431</v>
       </c>
       <c r="F32">
-        <v>4.144373233936556</v>
+        <v>4.490881753411045</v>
       </c>
       <c r="G32">
-        <v>-8.077483975574586</v>
+        <v>-8.200911044915232</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.315207573523465</v>
       </c>
       <c r="E33">
-        <v>-28.92263195090893</v>
+        <v>-27.87861038233656</v>
       </c>
       <c r="F33">
-        <v>4.097707755432217</v>
+        <v>4.444251116436846</v>
       </c>
       <c r="G33">
-        <v>-7.360959430691347</v>
+        <v>-8.457329349659483</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.387929294234747</v>
       </c>
       <c r="E34">
-        <v>-28.13320119104779</v>
+        <v>-29.34424646644506</v>
       </c>
       <c r="F34">
-        <v>4.112659522979881</v>
+        <v>3.805829171510811</v>
       </c>
       <c r="G34">
-        <v>-7.219330981975786</v>
+        <v>-8.103961718797676</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.507511482887175</v>
       </c>
       <c r="E35">
-        <v>-27.96487328370867</v>
+        <v>-27.64283991160121</v>
       </c>
       <c r="F35">
-        <v>4.45878636932875</v>
+        <v>3.879626699758459</v>
       </c>
       <c r="G35">
-        <v>-8.035257967221181</v>
+        <v>-7.755566527335855</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.666629531437664</v>
       </c>
       <c r="E36">
-        <v>-28.20102867473468</v>
+        <v>-28.73088730447616</v>
       </c>
       <c r="F36">
-        <v>4.420604803413419</v>
+        <v>3.851338544696879</v>
       </c>
       <c r="G36">
-        <v>-7.517382707421911</v>
+        <v>-7.621098788621738</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.858326527165192</v>
       </c>
       <c r="E37">
-        <v>-27.01070116792249</v>
+        <v>-27.70470339502</v>
       </c>
       <c r="F37">
-        <v>4.16885732738925</v>
+        <v>4.183790090465928</v>
       </c>
       <c r="G37">
-        <v>-6.992962499091501</v>
+        <v>-7.4668273664917</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.076537809337141</v>
       </c>
       <c r="E38">
-        <v>-27.71595212445505</v>
+        <v>-27.50730721302565</v>
       </c>
       <c r="F38">
-        <v>4.135219413745316</v>
+        <v>4.06567888699837</v>
       </c>
       <c r="G38">
-        <v>-8.081013017119448</v>
+        <v>-8.072041438708023</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.3208591119413</v>
       </c>
       <c r="E39">
-        <v>-26.82575376097523</v>
+        <v>-27.28943780004262</v>
       </c>
       <c r="F39">
-        <v>4.246533351423809</v>
+        <v>3.872664728554187</v>
       </c>
       <c r="G39">
-        <v>-7.193796744231387</v>
+        <v>-7.635602288629284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.580171468195052</v>
       </c>
       <c r="E40">
-        <v>-26.95217969832137</v>
+        <v>-26.35786276955471</v>
       </c>
       <c r="F40">
-        <v>3.962057008951167</v>
+        <v>3.996889036855342</v>
       </c>
       <c r="G40">
-        <v>-8.371731884196087</v>
+        <v>-7.639098224718755</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.854400141068474</v>
       </c>
       <c r="E41">
-        <v>-26.86822179021916</v>
+        <v>-28.32937468506007</v>
       </c>
       <c r="F41">
-        <v>4.011557321044142</v>
+        <v>3.988401956854502</v>
       </c>
       <c r="G41">
-        <v>-8.51107605648955</v>
+        <v>-7.970646049931225</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.139903694923992</v>
       </c>
       <c r="E42">
-        <v>-26.75780853696414</v>
+        <v>-26.34473019493247</v>
       </c>
       <c r="F42">
-        <v>3.919010298463607</v>
+        <v>4.294448373895428</v>
       </c>
       <c r="G42">
-        <v>-7.882549122585679</v>
+        <v>-7.985242245213872</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.434985218943423</v>
       </c>
       <c r="E43">
-        <v>-26.70900064410947</v>
+        <v>-25.4736918049791</v>
       </c>
       <c r="F43">
-        <v>4.444916272921331</v>
+        <v>4.217485017522818</v>
       </c>
       <c r="G43">
-        <v>-8.363289993070945</v>
+        <v>-8.421840301478495</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.734556825393506</v>
       </c>
       <c r="E44">
-        <v>-26.13597660012688</v>
+        <v>-25.0264189557155</v>
       </c>
       <c r="F44">
-        <v>4.189982380595296</v>
+        <v>3.955631914052229</v>
       </c>
       <c r="G44">
-        <v>-8.547548336695701</v>
+        <v>-6.824571600236473</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.039801604351796</v>
       </c>
       <c r="E45">
-        <v>-25.3167122535032</v>
+        <v>-23.19612750213934</v>
       </c>
       <c r="F45">
-        <v>4.451808561065323</v>
+        <v>4.105048232350279</v>
       </c>
       <c r="G45">
-        <v>-9.263218760829806</v>
+        <v>-7.986563152884041</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.353564011464934</v>
       </c>
       <c r="E46">
-        <v>-25.03635895616234</v>
+        <v>-23.48648872703716</v>
       </c>
       <c r="F46">
-        <v>4.20194094396278</v>
+        <v>3.867457503504222</v>
       </c>
       <c r="G46">
-        <v>-9.197663338061158</v>
+        <v>-8.850916798277895</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.668333456307707</v>
       </c>
       <c r="E47">
-        <v>-23.63840997304649</v>
+        <v>-22.79114154315938</v>
       </c>
       <c r="F47">
-        <v>4.442911301232384</v>
+        <v>3.874931011719181</v>
       </c>
       <c r="G47">
-        <v>-8.932425740000291</v>
+        <v>-8.848367678212655</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.985955963828122</v>
       </c>
       <c r="E48">
-        <v>-23.78595218469039</v>
+        <v>-21.88374856387243</v>
       </c>
       <c r="F48">
-        <v>4.848842050360077</v>
+        <v>4.666437137843423</v>
       </c>
       <c r="G48">
-        <v>-9.817116066641887</v>
+        <v>-8.92275563648008</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.30354754540442</v>
       </c>
       <c r="E49">
-        <v>-23.52131269215614</v>
+        <v>-23.03178918040098</v>
       </c>
       <c r="F49">
-        <v>4.132446344687382</v>
+        <v>4.221751521259012</v>
       </c>
       <c r="G49">
-        <v>-9.067006037262743</v>
+        <v>-10.24083941130428</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.62292429250569</v>
       </c>
       <c r="E50">
-        <v>-23.99468766559995</v>
+        <v>-22.65027430220277</v>
       </c>
       <c r="F50">
-        <v>4.260169059355742</v>
+        <v>4.64330711294843</v>
       </c>
       <c r="G50">
-        <v>-8.777644493857206</v>
+        <v>-9.194667294348118</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.93475521834261</v>
       </c>
       <c r="E51">
-        <v>-21.18103808125817</v>
+        <v>-22.81429563076059</v>
       </c>
       <c r="F51">
-        <v>4.919997957140771</v>
+        <v>4.183273802337495</v>
       </c>
       <c r="G51">
-        <v>-9.542936685079447</v>
+        <v>-9.784189380708296</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.24034554777234</v>
       </c>
       <c r="E52">
-        <v>-22.3649532688755</v>
+        <v>-21.34330236190102</v>
       </c>
       <c r="F52">
-        <v>4.526519887626179</v>
+        <v>4.192878978714635</v>
       </c>
       <c r="G52">
-        <v>-10.49733716914148</v>
+        <v>-9.870207285455178</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.53875881341779</v>
       </c>
       <c r="E53">
-        <v>-21.80612146243294</v>
+        <v>-21.41852031516842</v>
       </c>
       <c r="F53">
-        <v>4.51151427407739</v>
+        <v>4.437145027994269</v>
       </c>
       <c r="G53">
-        <v>-9.861838226331901</v>
+        <v>-9.585735417811145</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.8251256841758</v>
       </c>
       <c r="E54">
-        <v>-22.07809708285962</v>
+        <v>-19.8157846804777</v>
       </c>
       <c r="F54">
-        <v>4.337438070970032</v>
+        <v>3.9416889671727</v>
       </c>
       <c r="G54">
-        <v>-9.693986946399773</v>
+        <v>-9.94733306488358</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.0968034549803</v>
       </c>
       <c r="E55">
-        <v>-21.97867896449522</v>
+        <v>-19.0336447637689</v>
       </c>
       <c r="F55">
-        <v>4.039854978341214</v>
+        <v>3.744021880748956</v>
       </c>
       <c r="G55">
-        <v>-9.827428415996717</v>
+        <v>-9.720223019798498</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.35238963581115</v>
       </c>
       <c r="E56">
-        <v>-21.31994902144346</v>
+        <v>-19.94732779345251</v>
       </c>
       <c r="F56">
-        <v>4.26843442052842</v>
+        <v>3.709421073908435</v>
       </c>
       <c r="G56">
-        <v>-9.50063784472418</v>
+        <v>-10.6187977744318</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.5960546403204</v>
       </c>
       <c r="E57">
-        <v>-20.62511355512854</v>
+        <v>-18.85417228189691</v>
       </c>
       <c r="F57">
-        <v>4.176894634910105</v>
+        <v>4.284681659514914</v>
       </c>
       <c r="G57">
-        <v>-10.32890654373998</v>
+        <v>-9.421131783053042</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.8176576449735</v>
       </c>
       <c r="E58">
-        <v>-20.60303724434115</v>
+        <v>-18.64053246363705</v>
       </c>
       <c r="F58">
-        <v>4.143731833040803</v>
+        <v>3.726304962672935</v>
       </c>
       <c r="G58">
-        <v>-10.42294258978298</v>
+        <v>-10.88867344679318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.02108603768055</v>
       </c>
       <c r="E59">
-        <v>-20.58457465581188</v>
+        <v>-18.39061504010174</v>
       </c>
       <c r="F59">
-        <v>4.296703571119014</v>
+        <v>3.963170354209721</v>
       </c>
       <c r="G59">
-        <v>-10.55747322886234</v>
+        <v>-9.975317106327038</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.20320149290591</v>
       </c>
       <c r="E60">
-        <v>-18.94072047713151</v>
+        <v>-16.61554832704912</v>
       </c>
       <c r="F60">
-        <v>4.629275478537637</v>
+        <v>4.070422086215111</v>
       </c>
       <c r="G60">
-        <v>-10.05722662405969</v>
+        <v>-11.22127733603268</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.36622083111856</v>
       </c>
       <c r="E61">
-        <v>-19.12259305022756</v>
+        <v>-19.65991007665968</v>
       </c>
       <c r="F61">
-        <v>4.211753585814843</v>
+        <v>3.404370807888319</v>
       </c>
       <c r="G61">
-        <v>-10.58356363825733</v>
+        <v>-10.63812473929006</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.50408097273276</v>
       </c>
       <c r="E62">
-        <v>-18.79762069848913</v>
+        <v>-17.286745159044</v>
       </c>
       <c r="F62">
-        <v>4.385946983159942</v>
+        <v>3.77495799210115</v>
       </c>
       <c r="G62">
-        <v>-10.68728965109378</v>
+        <v>-11.5155517290185</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.61682968729567</v>
       </c>
       <c r="E63">
-        <v>-18.93031857233589</v>
+        <v>-17.08325817950933</v>
       </c>
       <c r="F63">
-        <v>4.090429043044858</v>
+        <v>3.448001905858677</v>
       </c>
       <c r="G63">
-        <v>-10.86739657061229</v>
+        <v>-9.966924873384986</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.70766952806065</v>
       </c>
       <c r="E64">
-        <v>-17.57494630184015</v>
+        <v>-16.68105270357007</v>
       </c>
       <c r="F64">
-        <v>3.928493529485258</v>
+        <v>3.915220490207961</v>
       </c>
       <c r="G64">
-        <v>-9.879519850057148</v>
+        <v>-12.50678203220492</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.77034184774109</v>
       </c>
       <c r="E65">
-        <v>-18.34757642313284</v>
+        <v>-16.87242148666021</v>
       </c>
       <c r="F65">
-        <v>4.161174769993453</v>
+        <v>3.242706108040261</v>
       </c>
       <c r="G65">
-        <v>-10.52624816333593</v>
+        <v>-10.85360814844123</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.80556015022003</v>
       </c>
       <c r="E66">
-        <v>-18.14533477395028</v>
+        <v>-16.64640082046338</v>
       </c>
       <c r="F66">
-        <v>3.770678818717633</v>
+        <v>3.206768653407109</v>
       </c>
       <c r="G66">
-        <v>-10.5375834712624</v>
+        <v>-9.768206066844694</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.80780063914347</v>
       </c>
       <c r="E67">
-        <v>-18.09134177835682</v>
+        <v>-16.86169806021005</v>
       </c>
       <c r="F67">
-        <v>4.065195856694161</v>
+        <v>3.366431548978052</v>
       </c>
       <c r="G67">
-        <v>-10.20660174933714</v>
+        <v>-11.17911091749898</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.78279801401303</v>
       </c>
       <c r="E68">
-        <v>-17.76296401416462</v>
+        <v>-16.53842841469849</v>
       </c>
       <c r="F68">
-        <v>3.68637498542696</v>
+        <v>3.126333813667855</v>
       </c>
       <c r="G68">
-        <v>-11.10706020438229</v>
+        <v>-11.19897088018907</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.72216221660405</v>
       </c>
       <c r="E69">
-        <v>-17.10976333787622</v>
+        <v>-16.23277000460277</v>
       </c>
       <c r="F69">
-        <v>3.867731484627593</v>
+        <v>3.346817351215335</v>
       </c>
       <c r="G69">
-        <v>-10.31426400081978</v>
+        <v>-12.06710847913431</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.62626171896038</v>
       </c>
       <c r="E70">
-        <v>-17.17726477143456</v>
+        <v>-16.71469020849904</v>
       </c>
       <c r="F70">
-        <v>3.722146150938991</v>
+        <v>3.165180536067669</v>
       </c>
       <c r="G70">
-        <v>-10.90942725677888</v>
+        <v>-11.29301023677761</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.49495161532889</v>
       </c>
       <c r="E71">
-        <v>-18.11531551975343</v>
+        <v>-17.16471184148529</v>
       </c>
       <c r="F71">
-        <v>3.318445259740237</v>
+        <v>3.639757018100085</v>
       </c>
       <c r="G71">
-        <v>-11.06424822946843</v>
+        <v>-10.94314847364189</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.33017773441452</v>
       </c>
       <c r="E72">
-        <v>-17.36109817377594</v>
+        <v>-16.19634748815907</v>
       </c>
       <c r="F72">
-        <v>3.405979853098406</v>
+        <v>3.075511107135488</v>
       </c>
       <c r="G72">
-        <v>-11.02112837381942</v>
+        <v>-10.94962390071671</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.13101688126575</v>
       </c>
       <c r="E73">
-        <v>-17.3438356308587</v>
+        <v>-15.49389965703726</v>
       </c>
       <c r="F73">
-        <v>3.288586068410542</v>
+        <v>2.782645874428763</v>
       </c>
       <c r="G73">
-        <v>-11.0060951865256</v>
+        <v>-11.12450346882871</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.89739132147335</v>
       </c>
       <c r="E74">
-        <v>-17.59293340059862</v>
+        <v>-17.14704173590737</v>
       </c>
       <c r="F74">
-        <v>3.857576762297795</v>
+        <v>2.810064574942766</v>
       </c>
       <c r="G74">
-        <v>-10.69530448184435</v>
+        <v>-10.80165906783898</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.64051440193417</v>
       </c>
       <c r="E75">
-        <v>-17.75072807739589</v>
+        <v>-16.57459733659775</v>
       </c>
       <c r="F75">
-        <v>3.190288609651046</v>
+        <v>2.841433038009876</v>
       </c>
       <c r="G75">
-        <v>-10.15131563883131</v>
+        <v>-11.56120415200505</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.36007059162599</v>
       </c>
       <c r="E76">
-        <v>-18.16776883418428</v>
+        <v>-16.19256168388866</v>
       </c>
       <c r="F76">
-        <v>3.522553278122073</v>
+        <v>2.372847715455567</v>
       </c>
       <c r="G76">
-        <v>-10.04978120714187</v>
+        <v>-10.68377054118553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.06517667229394</v>
       </c>
       <c r="E77">
-        <v>-18.34950555306011</v>
+        <v>-16.15567726309618</v>
       </c>
       <c r="F77">
-        <v>3.053336056907504</v>
+        <v>3.138944863872499</v>
       </c>
       <c r="G77">
-        <v>-10.04317997933656</v>
+        <v>-10.27684821513494</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.75877422528926</v>
       </c>
       <c r="E78">
-        <v>-19.41444867154791</v>
+        <v>-18.4631521367566</v>
       </c>
       <c r="F78">
-        <v>3.057526542759757</v>
+        <v>2.582231058241732</v>
       </c>
       <c r="G78">
-        <v>-10.14396953827967</v>
+        <v>-10.32111683008607</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.45619627347229</v>
       </c>
       <c r="E79">
-        <v>-19.41975151461089</v>
+        <v>-18.15233126629213</v>
       </c>
       <c r="F79">
-        <v>2.827442579952884</v>
+        <v>2.720713470899588</v>
       </c>
       <c r="G79">
-        <v>-9.516399352036649</v>
+        <v>-10.22957362483415</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.16045050308128</v>
       </c>
       <c r="E80">
-        <v>-20.01935770101851</v>
+        <v>-18.63103625364296</v>
       </c>
       <c r="F80">
-        <v>3.307568367512999</v>
+        <v>2.611727580916792</v>
       </c>
       <c r="G80">
-        <v>-9.211190227134621</v>
+        <v>-9.92298400244224</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.87755325843575</v>
       </c>
       <c r="E81">
-        <v>-20.56929105603599</v>
+        <v>-19.18708757704481</v>
       </c>
       <c r="F81">
-        <v>3.050471132906474</v>
+        <v>2.691210613400866</v>
       </c>
       <c r="G81">
-        <v>-10.18467269568501</v>
+        <v>-10.2421470767923</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.61782476449487</v>
       </c>
       <c r="E82">
-        <v>-22.42443477496624</v>
+        <v>-21.67383567972088</v>
       </c>
       <c r="F82">
-        <v>3.162008373119044</v>
+        <v>3.008289125848745</v>
       </c>
       <c r="G82">
-        <v>-9.531521924060041</v>
+        <v>-9.382775802435047</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.38493491493634</v>
       </c>
       <c r="E83">
-        <v>-21.84315532286767</v>
+        <v>-20.48310966719602</v>
       </c>
       <c r="F83">
-        <v>3.363818434217577</v>
+        <v>2.823793721523711</v>
       </c>
       <c r="G83">
-        <v>-9.367745925686755</v>
+        <v>-8.766305875385202</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.18206877864001</v>
       </c>
       <c r="E84">
-        <v>-22.19135874626546</v>
+        <v>-22.12464979565847</v>
       </c>
       <c r="F84">
-        <v>2.726859833557409</v>
+        <v>2.838583951068</v>
       </c>
       <c r="G84">
-        <v>-8.822740745193158</v>
+        <v>-8.35136540803849</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.00580828096726</v>
       </c>
       <c r="E85">
-        <v>-22.78587039941445</v>
+        <v>-23.02754147178179</v>
       </c>
       <c r="F85">
-        <v>2.767464469523361</v>
+        <v>2.771691380611669</v>
       </c>
       <c r="G85">
-        <v>-8.939811567098404</v>
+        <v>-9.052903113265447</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.862295520795955</v>
       </c>
       <c r="E86">
-        <v>-24.35664406455903</v>
+        <v>-24.34757353112167</v>
       </c>
       <c r="F86">
-        <v>2.851362874099681</v>
+        <v>2.394504893849202</v>
       </c>
       <c r="G86">
-        <v>-8.806161533132487</v>
+        <v>-6.733925552825688</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.742507750343114</v>
       </c>
       <c r="E87">
-        <v>-27.11531797444769</v>
+        <v>-25.83067141100375</v>
       </c>
       <c r="F87">
-        <v>2.996626715487448</v>
+        <v>3.162428055186635</v>
       </c>
       <c r="G87">
-        <v>-8.705967872386445</v>
+        <v>-7.280248330443915</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.641034708546009</v>
       </c>
       <c r="E88">
-        <v>-27.2244270271885</v>
+        <v>-26.72409404797704</v>
       </c>
       <c r="F88">
-        <v>2.894759583594552</v>
+        <v>2.586575163567782</v>
       </c>
       <c r="G88">
-        <v>-8.439200802286434</v>
+        <v>-8.647225552337616</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.549766082316072</v>
       </c>
       <c r="E89">
-        <v>-27.71124251148707</v>
+        <v>-28.96826991195823</v>
       </c>
       <c r="F89">
-        <v>2.820171786095101</v>
+        <v>2.790312594765405</v>
       </c>
       <c r="G89">
-        <v>-8.174506133694006</v>
+        <v>-8.343092354735852</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.462982087216563</v>
       </c>
       <c r="E90">
-        <v>-30.46208668981647</v>
+        <v>-29.03148288063131</v>
       </c>
       <c r="F90">
-        <v>2.693114227911225</v>
+        <v>2.542323252878573</v>
       </c>
       <c r="G90">
-        <v>-7.406618474768975</v>
+        <v>-7.433867575102717</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.369032554560818</v>
       </c>
       <c r="E91">
-        <v>-30.20769513396158</v>
+        <v>-31.89650347411609</v>
       </c>
       <c r="F91">
-        <v>2.748597780952731</v>
+        <v>2.990455013534981</v>
       </c>
       <c r="G91">
-        <v>-7.532008697614411</v>
+        <v>-7.740066553120987</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.256412409782087</v>
       </c>
       <c r="E92">
-        <v>-33.19227423395988</v>
+        <v>-36.65332578362323</v>
       </c>
       <c r="F92">
-        <v>2.882609391811301</v>
+        <v>2.93862665374631</v>
       </c>
       <c r="G92">
-        <v>-7.503398963064029</v>
+        <v>-7.355599657463267</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.122046633793198</v>
       </c>
       <c r="E93">
-        <v>-34.81370114511726</v>
+        <v>-36.9350398874034</v>
       </c>
       <c r="F93">
-        <v>2.521278968674214</v>
+        <v>2.318064160428686</v>
       </c>
       <c r="G93">
-        <v>-7.26782716358057</v>
+        <v>-7.353792099598825</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.955813496168576</v>
       </c>
       <c r="E94">
-        <v>-36.5453262070143</v>
+        <v>-37.03496519485665</v>
       </c>
       <c r="F94">
-        <v>2.498798263204551</v>
+        <v>2.336991029824103</v>
       </c>
       <c r="G94">
-        <v>-7.639905997830337</v>
+        <v>-6.534471805175677</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.755130485480583</v>
       </c>
       <c r="E95">
-        <v>-38.21202200858936</v>
+        <v>-39.96967221060848</v>
       </c>
       <c r="F95">
-        <v>2.608599761733799</v>
+        <v>2.567529516228708</v>
       </c>
       <c r="G95">
-        <v>-7.329297373153757</v>
+        <v>-7.023555250419906</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.511908454815394</v>
       </c>
       <c r="E96">
-        <v>-40.3193677661918</v>
+        <v>-41.52739028518895</v>
       </c>
       <c r="F96">
-        <v>2.397732486504867</v>
+        <v>2.482395821038345</v>
       </c>
       <c r="G96">
-        <v>-6.89258344779526</v>
+        <v>-7.240909117800756</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.235274329737521</v>
       </c>
       <c r="E97">
-        <v>-43.29055616854941</v>
+        <v>-44.3316319647798</v>
       </c>
       <c r="F97">
-        <v>2.291888669058303</v>
+        <v>2.740403686546247</v>
       </c>
       <c r="G97">
-        <v>-8.267244445885609</v>
+        <v>-7.72183868938176</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.918792064906018</v>
       </c>
       <c r="E98">
-        <v>-44.5185515221574</v>
+        <v>-46.41156007650279</v>
       </c>
       <c r="F98">
-        <v>2.308573010877457</v>
+        <v>2.221103349461821</v>
       </c>
       <c r="G98">
-        <v>-7.016109833502085</v>
+        <v>-8.251900067311087</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.573812537531544</v>
       </c>
       <c r="E99">
-        <v>-46.97788650742803</v>
+        <v>-48.6533199996009</v>
       </c>
       <c r="F99">
-        <v>2.369970121807214</v>
+        <v>2.206851579928781</v>
       </c>
       <c r="G99">
-        <v>-7.02553826719793</v>
+        <v>-7.325291613051239</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.195088638439721</v>
       </c>
       <c r="E100">
-        <v>-48.529398308381</v>
+        <v>-49.7641976941855</v>
       </c>
       <c r="F100">
-        <v>1.971554057248281</v>
+        <v>2.539645206175565</v>
       </c>
       <c r="G100">
-        <v>-7.459246217206769</v>
+        <v>-7.933223643155304</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.810631662721319</v>
       </c>
       <c r="E101">
-        <v>-50.83253603606057</v>
+        <v>-53.18776140389486</v>
       </c>
       <c r="F101">
-        <v>1.683588810643926</v>
+        <v>2.099218174797771</v>
       </c>
       <c r="G101">
-        <v>-7.256203838192189</v>
+        <v>-7.122944448599906</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.391990443360514</v>
       </c>
       <c r="E102">
-        <v>-51.96447905961035</v>
+        <v>-55.16947144286549</v>
       </c>
       <c r="F102">
-        <v>1.798486674809058</v>
+        <v>1.861644866716783</v>
       </c>
       <c r="G102">
-        <v>-8.730869795932843</v>
+        <v>-7.822187945768148</v>
       </c>
     </row>
   </sheetData>
